--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -413,155 +413,235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>product</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>profit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>user_email</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>50000</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>10000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ashwanyadav6612@gmail.com</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>South</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>30000</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>5000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ashwanyadav6612@gmail.com</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>25000</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>4000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ashwanyadav6612@gmail.com</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>60000</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>12000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ashwanyadav6612@gmail.com</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>45000</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>7000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ashwanyadav6612@gmail.com</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Camera</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>South</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>35000</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>6000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ashwanyadav6612@gmail.com</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>55000</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>8000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ashwanyadav6612@gmail.com</t>
+        </is>
       </c>
     </row>
   </sheetData>
